--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/desktop/desktop_grid_pref.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/desktop/desktop_grid_pref.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C2" t="n">
-        <v>33.5</v>
+        <v>33.04</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>24.11</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>20.98</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C5" t="n">
-        <v>16.5</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
     </row>
   </sheetData>
